--- a/artfynd/A 38689-2021 artfynd.xlsx
+++ b/artfynd/A 38689-2021 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 38689-2021 artfynd.xlsx
+++ b/artfynd/A 38689-2021 artfynd.xlsx
@@ -678,12 +678,7 @@
         <v>14972780</v>
       </c>
       <c r="B2" t="n">
-        <v>12379</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>12494</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -734,10 +729,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>750750.0769943207</v>
+        <v>750750</v>
       </c>
       <c r="R2" t="n">
-        <v>7089725.871349527</v>
+        <v>7089726</v>
       </c>
       <c r="S2" t="n">
         <v>50</v>
@@ -767,19 +762,9 @@
           <t>2011-06-03</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2011-07-10</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
@@ -825,12 +810,7 @@
         <v>14972781</v>
       </c>
       <c r="B3" t="n">
-        <v>12255</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>12370</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -881,10 +861,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>750750.0769943207</v>
+        <v>750750</v>
       </c>
       <c r="R3" t="n">
-        <v>7089725.871349527</v>
+        <v>7089726</v>
       </c>
       <c r="S3" t="n">
         <v>50</v>
@@ -914,19 +894,9 @@
           <t>2011-06-03</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2011-07-10</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
